--- a/exports/ABB_full_report.xlsx
+++ b/exports/ABB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.32</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44586.55208333334</v>
+        <v>44588.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>2400</v>
+        <v>2232.85</v>
       </c>
       <c r="I2" t="n">
         <v>2254.112759127023</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>6.57</v>
+        <v>-0.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.29</v>
+        <v>5.15</v>
       </c>
       <c r="M2" t="n">
         <v>0.88</v>
       </c>
       <c r="N2" t="n">
-        <v>1.81</v>
+        <v>7.42</v>
       </c>
       <c r="O2" t="n">
         <v>2.82</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.91</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44622.55208333334</v>
+        <v>44623.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>2181</v>
+        <v>2222.2</v>
       </c>
       <c r="I3" t="n">
         <v>2212.044027133826</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K3" t="n">
-        <v>2.32</v>
+        <v>0.48</v>
       </c>
       <c r="L3" t="n">
         <v>7.71</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.57</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44634.55208333334</v>
+        <v>44635.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>2064</v>
+        <v>2053.05</v>
       </c>
       <c r="I4" t="n">
         <v>2053.874454304579</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.12</v>
+        <v>-7.61</v>
       </c>
       <c r="L4" t="n">
-        <v>7.14</v>
+        <v>8.15</v>
       </c>
       <c r="M4" t="n">
         <v>0.92</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.04</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44651.38541666666</v>
+        <v>44651.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>2097.8</v>
+        <v>2140</v>
       </c>
       <c r="I5" t="n">
         <v>2118.179285860353</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.18</v>
+        <v>-4.24</v>
       </c>
       <c r="L5" t="n">
         <v>7.55</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.57</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44676.55208333334</v>
+        <v>44677.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>2100</v>
+        <v>2091.15</v>
       </c>
       <c r="I6" t="n">
         <v>2096.02813950463</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.87</v>
+        <v>-2.28</v>
       </c>
       <c r="L6" t="n">
-        <v>2.57</v>
+        <v>3.62</v>
       </c>
       <c r="M6" t="n">
         <v>1.46</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>7.45</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44685.55208333334</v>
+        <v>44686.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2020.85</v>
+        <v>2227</v>
       </c>
       <c r="I7" t="n">
         <v>2159.558788117624</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>3.36</v>
+        <v>-6.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.78</v>
+        <v>7.49</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2</v>
+        <v>3.86</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8</v>
+        <v>10.05</v>
       </c>
       <c r="O7" t="n">
         <v>-0.24</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.08</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>2300.1</v>
+        <v>2217.5</v>
       </c>
       <c r="I8" t="n">
         <v>2266.941485154657</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K8" t="n">
-        <v>3.28</v>
+        <v>-0.43</v>
       </c>
       <c r="L8" t="n">
         <v>6.41</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>10.99</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44747.55208333334</v>
+        <v>44748.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>2366</v>
+        <v>2495.65</v>
       </c>
       <c r="I9" t="n">
         <v>2376.543993498583</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.7</v>
+        <v>-12.54</v>
       </c>
       <c r="L9" t="n">
-        <v>8.460000000000001</v>
+        <v>14.05</v>
       </c>
       <c r="M9" t="n">
         <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>3.46</v>
+        <v>6.85</v>
       </c>
       <c r="O9" t="n">
         <v>-2.79</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.06</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>3290</v>
+        <v>3175</v>
       </c>
       <c r="I10" t="n">
         <v>3211.470313286311</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>71.16666666666667</v>
+        <v>72</v>
       </c>
       <c r="K10" t="n">
-        <v>31.83</v>
+        <v>27.22</v>
       </c>
       <c r="L10" t="n">
         <v>5.03</v>
@@ -1011,7 +1130,7 @@
         <v>1.2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.73</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
         <v>6.85</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.43</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>3079.85</v>
+        <v>3208.8</v>
       </c>
       <c r="I11" t="n">
         <v>3197.658345571934</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>-1.06</v>
       </c>
       <c r="L11" t="n">
         <v>4.41</v>
@@ -1068,7 +1199,7 @@
         <v>2.05</v>
       </c>
       <c r="N11" t="n">
-        <v>2.73</v>
+        <v>3.77</v>
       </c>
       <c r="O11" t="n">
         <v>-3.8</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.34</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44854.55208333334</v>
+        <v>44855.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>3126.3</v>
+        <v>3081.6</v>
       </c>
       <c r="I12" t="n">
         <v>3098.233627982715</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.57</v>
+        <v>-3.96</v>
       </c>
       <c r="L12" t="n">
         <v>4.22</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.33</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44866.55208333334</v>
+        <v>44867.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>3146.3</v>
+        <v>3170.6</v>
       </c>
       <c r="I13" t="n">
         <v>3165.874030314294</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.1</v>
+        <v>-2.89</v>
       </c>
       <c r="L13" t="n">
         <v>3.65</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.76</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44876.55208333334</v>
+        <v>44879.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>3139.9</v>
+        <v>3037.05</v>
       </c>
       <c r="I14" t="n">
         <v>3074.056965649699</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.97</v>
+        <v>-4.21</v>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>5.01</v>
       </c>
       <c r="M14" t="n">
         <v>0.41</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.62</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44931.38541666666</v>
+        <v>44931.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>2766.45</v>
+        <v>2811</v>
       </c>
       <c r="I15" t="n">
         <v>2800.746364520071</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>8.91</v>
+        <v>7.44</v>
       </c>
       <c r="L15" t="n">
         <v>5.81</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>5.12</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>2880.45</v>
+        <v>2778</v>
       </c>
       <c r="I16" t="n">
         <v>2841.153932869679</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>2.47</v>
+        <v>-1.17</v>
       </c>
       <c r="L16" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="M16" t="n">
         <v>0.25</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.83</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44963.38541666666</v>
+        <v>44963.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>2810.7</v>
+        <v>2930</v>
       </c>
       <c r="I17" t="n">
         <v>2929.972999644204</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.18</v>
+        <v>-5.47</v>
       </c>
       <c r="L17" t="n">
         <v>6.63</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45027.55208333334</v>
+        <v>45028.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>3280</v>
+        <v>3205.95</v>
       </c>
       <c r="I18" t="n">
         <v>3249.646569674914</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>64</v>
+        <v>64.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>11.95</v>
+        <v>9.42</v>
       </c>
       <c r="L18" t="n">
         <v>4.1</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>7.09</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45040.55208333334</v>
+        <v>45041.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>3223.1</v>
+        <v>3342.8</v>
       </c>
       <c r="I19" t="n">
         <v>3286.455537928547</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.53</v>
+        <v>-4.27</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>4.31</v>
       </c>
       <c r="M19" t="n">
         <v>0.83</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>3.69</v>
       </c>
       <c r="O19" t="n">
         <v>-2.44</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.8</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45126.55208333334</v>
+        <v>45127.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>4498.7</v>
+        <v>4198.5</v>
       </c>
       <c r="I20" t="n">
         <v>4335.296667499887</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>85.16666666666667</v>
+        <v>86</v>
       </c>
       <c r="K20" t="n">
-        <v>34.58</v>
+        <v>25.6</v>
       </c>
       <c r="L20" t="n">
         <v>3.97</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>10.07</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45134.55208333334</v>
+        <v>45135.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>4420</v>
+        <v>4518.9</v>
       </c>
       <c r="I21" t="n">
         <v>4480.975604392584</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.28</v>
+        <v>-7.63</v>
       </c>
       <c r="L21" t="n">
-        <v>7.3</v>
+        <v>7.89</v>
       </c>
       <c r="M21" t="n">
         <v>0.51</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="O21" t="n">
         <v>-6.55</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.66</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45152.55208333334</v>
+        <v>45154.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>4348.9</v>
+        <v>4300</v>
       </c>
       <c r="I22" t="n">
         <v>4325.558129055369</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.76</v>
+        <v>-4.84</v>
       </c>
       <c r="L22" t="n">
         <v>5.86</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>6.86</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45174.55208333334</v>
+        <v>45175.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>4443.2</v>
+        <v>4485</v>
       </c>
       <c r="I23" t="n">
         <v>4445.541193649427</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.33</v>
+        <v>-4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>3.49</v>
+        <v>5.58</v>
       </c>
       <c r="M23" t="n">
         <v>0.8100000000000001</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>4.38</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>4620</v>
+        <v>4403.65</v>
       </c>
       <c r="I24" t="n">
         <v>4407.668793022573</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.01</v>
+        <v>-1.81</v>
       </c>
       <c r="L24" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="M24" t="n">
         <v>-0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.96</v>
+        <v>4.81</v>
       </c>
       <c r="O24" t="n">
         <v>1.01</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.67</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45210.55208333334</v>
+        <v>45211.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>4170.1</v>
+        <v>4212.15</v>
       </c>
       <c r="I25" t="n">
         <v>4194.541830314383</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>5.3</v>
+        <v>4.35</v>
       </c>
       <c r="L25" t="n">
         <v>5.41</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>4.07</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45216.55208333334</v>
+        <v>45217.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>4275</v>
+        <v>4125</v>
       </c>
       <c r="I26" t="n">
         <v>4142.004980757098</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
-        <v>1.49</v>
+        <v>-2.07</v>
       </c>
       <c r="L26" t="n">
-        <v>0.53</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
         <v>0.45</v>
       </c>
       <c r="N26" t="n">
-        <v>0.12</v>
+        <v>4.28</v>
       </c>
       <c r="O26" t="n">
         <v>1.17</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.23</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45230.38541666666</v>
+        <v>45230.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>4082.15</v>
+        <v>4113</v>
       </c>
       <c r="I27" t="n">
         <v>4105.553892470629</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="L27" t="n">
         <v>5.2</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>5.39</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>4799.85</v>
+        <v>4592.4</v>
       </c>
       <c r="I28" t="n">
         <v>4653.176596180072</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>49.83333333333334</v>
+        <v>50</v>
       </c>
       <c r="K28" t="n">
-        <v>16.7</v>
+        <v>11.66</v>
       </c>
       <c r="L28" t="n">
         <v>1.66</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>8.81</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45299.55208333334</v>
+        <v>45300.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>4747.8</v>
+        <v>4934</v>
       </c>
       <c r="I29" t="n">
         <v>4882.628224296078</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.38</v>
+        <v>-7.44</v>
       </c>
       <c r="L29" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>0.88</v>
       </c>
       <c r="N29" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
         <v>-5.12</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.68</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>4726.95</v>
+        <v>4660.95</v>
       </c>
       <c r="I30" t="n">
         <v>4679.780900190335</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.2</v>
+        <v>-5.53</v>
       </c>
       <c r="L30" t="n">
         <v>6.49</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>6.89</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45342.55208333334</v>
+        <v>45343.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>4528.85</v>
+        <v>4956</v>
       </c>
       <c r="I31" t="n">
         <v>4687.470942201762</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K31" t="n">
-        <v>2.83</v>
+        <v>-6.33</v>
       </c>
       <c r="L31" t="n">
-        <v>2.18</v>
+        <v>6.49</v>
       </c>
       <c r="M31" t="n">
-        <v>1.03</v>
+        <v>2.45</v>
       </c>
       <c r="N31" t="n">
-        <v>3.47</v>
+        <v>10.62</v>
       </c>
       <c r="O31" t="n">
         <v>-1.42</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.91</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45400.38541666666</v>
+        <v>45400.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>6527</v>
+        <v>6400</v>
       </c>
       <c r="I32" t="n">
         <v>6461.67949289588</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>31.7</v>
+        <v>29.14</v>
       </c>
       <c r="L32" t="n">
         <v>6.38</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>6.61</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45412.55208333334</v>
+        <v>45414.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>6533.35</v>
+        <v>6672</v>
       </c>
       <c r="I33" t="n">
         <v>6662.999393435396</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>12</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.08</v>
+        <v>-4.25</v>
       </c>
       <c r="L33" t="n">
-        <v>3.79</v>
+        <v>5.44</v>
       </c>
       <c r="M33" t="n">
         <v>1.24</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.72</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>8700</v>
+        <v>7600.05</v>
       </c>
       <c r="I34" t="n">
         <v>8268.393173907854</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K34" t="n">
-        <v>30.4</v>
+        <v>13.91</v>
       </c>
       <c r="L34" t="n">
         <v>1.9</v>
@@ -2379,7 +2786,7 @@
         <v>1.19</v>
       </c>
       <c r="N34" t="n">
-        <v>1.81</v>
+        <v>11.7</v>
       </c>
       <c r="O34" t="n">
         <v>2.52</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>15.97</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45456.55208333334</v>
+        <v>45457.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>8443</v>
+        <v>9070</v>
       </c>
       <c r="I35" t="n">
         <v>8577.813529134639</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>-11.09</v>
+        <v>-19.34</v>
       </c>
       <c r="L35" t="n">
-        <v>15.13</v>
+        <v>20.33</v>
       </c>
       <c r="M35" t="n">
         <v>2.18</v>
       </c>
       <c r="N35" t="n">
-        <v>2.32</v>
+        <v>6.96</v>
       </c>
       <c r="O35" t="n">
         <v>-11.7</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>11.25</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45484.55208333334</v>
+        <v>45485.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>8470</v>
+        <v>8220</v>
       </c>
       <c r="I36" t="n">
         <v>8327.045567894107</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K36" t="n">
-        <v>-6.62</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="M36" t="n">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="N36" t="n">
         <v>3.61</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.93</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45511.38541666666</v>
+        <v>45511.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>7820.2</v>
+        <v>7887.1</v>
       </c>
       <c r="I37" t="n">
         <v>7872.403467718945</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>4.86</v>
+        <v>4.05</v>
       </c>
       <c r="L37" t="n">
         <v>3.41</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.21</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>7632</v>
+        <v>7544</v>
       </c>
       <c r="I38" t="n">
         <v>7597.880321237111</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.23</v>
+        <v>-4.35</v>
       </c>
       <c r="L38" t="n">
         <v>5.53</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>4.85</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>7698</v>
+        <v>7838.1</v>
       </c>
       <c r="I39" t="n">
         <v>7801.327526800576</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.04</v>
+        <v>-3.9</v>
       </c>
       <c r="L39" t="n">
-        <v>4.32</v>
+        <v>4.68</v>
       </c>
       <c r="M39" t="n">
         <v>0.95</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>4.98</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>7769</v>
+        <v>7411.6</v>
       </c>
       <c r="I40" t="n">
         <v>7520.077951196098</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.88</v>
+        <v>-5.44</v>
       </c>
       <c r="L40" t="n">
-        <v>1.77</v>
+        <v>6.23</v>
       </c>
       <c r="M40" t="n">
         <v>0.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.25</v>
+        <v>3.14</v>
       </c>
       <c r="O40" t="n">
         <v>0.9399999999999999</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.4</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45555.55208333334</v>
+        <v>45558.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>7744</v>
+        <v>7924.3</v>
       </c>
       <c r="I41" t="n">
         <v>7896.95464372024</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.48</v>
+        <v>-6.92</v>
       </c>
       <c r="L41" t="n">
-        <v>5.68</v>
+        <v>7.39</v>
       </c>
       <c r="M41" t="n">
         <v>0.79</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>6.79</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>7950</v>
+        <v>7744.75</v>
       </c>
       <c r="I42" t="n">
         <v>7827.965940475684</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>0.32</v>
+        <v>-2.27</v>
       </c>
       <c r="L42" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="M42" t="n">
         <v>1.85</v>
       </c>
       <c r="N42" t="n">
-        <v>2.07</v>
+        <v>2.59</v>
       </c>
       <c r="O42" t="n">
         <v>2.6</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>8.35</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>8129.1</v>
+        <v>8450</v>
       </c>
       <c r="I43" t="n">
         <v>8210.054097152663</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.96</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>5.58</v>
+        <v>10.78</v>
       </c>
       <c r="M43" t="n">
         <v>0.34</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45586.38541666666</v>
+        <v>45586.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>8364.9</v>
+        <v>8283.15</v>
       </c>
       <c r="I44" t="n">
         <v>8343.208502619333</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.01</v>
+        <v>-1.97</v>
       </c>
       <c r="L44" t="n">
         <v>4.37</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>8.06</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>6910</v>
+        <v>7217</v>
       </c>
       <c r="I45" t="n">
         <v>7113.675081759629</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>32</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>16.58</v>
+        <v>12.87</v>
       </c>
       <c r="L45" t="n">
         <v>1.4</v>
       </c>
       <c r="M45" t="n">
-        <v>0.98</v>
+        <v>2.6</v>
       </c>
       <c r="N45" t="n">
-        <v>3.06</v>
+        <v>4.95</v>
       </c>
       <c r="O45" t="n">
         <v>-5.64</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.5</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>7663.5</v>
+        <v>7388.8</v>
       </c>
       <c r="I46" t="n">
         <v>7577.455305297751</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>6.19</v>
+        <v>2.38</v>
       </c>
       <c r="L46" t="n">
         <v>2.3</v>
@@ -3063,7 +3614,7 @@
         <v>0.74</v>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>4.18</v>
       </c>
       <c r="O46" t="n">
         <v>4.95</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.53</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45674.38541666666</v>
+        <v>45674.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>6513.9</v>
+        <v>6525</v>
       </c>
       <c r="I47" t="n">
         <v>6523.07129231384</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>11.84</v>
+        <v>11.69</v>
       </c>
       <c r="L47" t="n">
         <v>3.13</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>5.84</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>6310.3</v>
+        <v>6160</v>
       </c>
       <c r="I48" t="n">
         <v>6175.538781425817</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.29</v>
+        <v>-5.59</v>
       </c>
       <c r="L48" t="n">
-        <v>4.01</v>
+        <v>5.85</v>
       </c>
       <c r="M48" t="n">
         <v>0.02</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.74</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45722.38541666666</v>
+        <v>45722.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>5337.05</v>
+        <v>5356.35</v>
       </c>
       <c r="I49" t="n">
         <v>5356.139195205355</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K49" t="n">
-        <v>13.36</v>
+        <v>13.05</v>
       </c>
       <c r="L49" t="n">
         <v>5.34</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.92</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>5330</v>
+        <v>5137.05</v>
       </c>
       <c r="I50" t="n">
         <v>5232.728260451687</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.49</v>
+        <v>-4.09</v>
       </c>
       <c r="L50" t="n">
         <v>6</v>
@@ -3291,7 +3890,7 @@
         <v>2.57</v>
       </c>
       <c r="N50" t="n">
-        <v>3.47</v>
+        <v>4.52</v>
       </c>
       <c r="O50" t="n">
         <v>0.7</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>8.43</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>5240</v>
+        <v>5382</v>
       </c>
       <c r="I51" t="n">
         <v>5280.645856095209</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K51" t="n">
-        <v>-2</v>
+        <v>-4.77</v>
       </c>
       <c r="L51" t="n">
-        <v>3.78</v>
+        <v>6.24</v>
       </c>
       <c r="M51" t="n">
         <v>2.26</v>
       </c>
       <c r="N51" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="O51" t="n">
         <v>-4.52</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.32</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>5382</v>
+        <v>5329</v>
       </c>
       <c r="I52" t="n">
         <v>5357.82587080517</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="L52" t="n">
         <v>2.41</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.1</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45789.55208333334</v>
+        <v>45790.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>5575</v>
+        <v>5680</v>
       </c>
       <c r="I53" t="n">
         <v>5634.840069899744</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.62</v>
+        <v>-6.59</v>
       </c>
       <c r="L53" t="n">
         <v>7.24</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>6020</v>
+        <v>5950</v>
       </c>
       <c r="I54" t="n">
         <v>5963.988991880255</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K54" t="n">
-        <v>5.99</v>
+        <v>4.75</v>
       </c>
       <c r="L54" t="n">
         <v>2.68</v>
       </c>
       <c r="M54" t="n">
-        <v>0.14</v>
+        <v>2.16</v>
       </c>
       <c r="N54" t="n">
         <v>1.59</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.18</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45859.38541666666</v>
+        <v>45859.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>5784</v>
+        <v>5835</v>
       </c>
       <c r="I55" t="n">
         <v>5791.146659615855</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>2.79</v>
+        <v>1.93</v>
       </c>
       <c r="L55" t="n">
         <v>3.78</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.2</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45869.38541666666</v>
+        <v>45869.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>5559</v>
+        <v>5514</v>
       </c>
       <c r="I56" t="n">
         <v>5531.617506817091</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.73</v>
+        <v>-5.5</v>
       </c>
       <c r="L56" t="n">
         <v>6.26</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.47</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45902.55208333334</v>
+        <v>45903.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>5150</v>
+        <v>5185.3</v>
       </c>
       <c r="I57" t="n">
         <v>5171.522431416648</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K57" t="n">
-        <v>6.6</v>
+        <v>5.96</v>
       </c>
       <c r="L57" t="n">
         <v>0.87</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>3.76</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45924.38541666666</v>
+        <v>45924.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>5281.2</v>
+        <v>5240</v>
       </c>
       <c r="I58" t="n">
         <v>5274.767669342045</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="L58" t="n">
         <v>2.22</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>3.98</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45959.38541666666</v>
+        <v>45959.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>5270</v>
+        <v>5300</v>
       </c>
       <c r="I59" t="n">
         <v>5297.418321656018</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>34.83333333333334</v>
+        <v>35</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.57</v>
+        <v>-1.15</v>
       </c>
       <c r="L59" t="n">
         <v>1.97</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>3.91</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45967.55208333334</v>
+        <v>45968.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>5205</v>
+        <v>5005.5</v>
       </c>
       <c r="I60" t="n">
         <v>5092.919625287907</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.79</v>
+        <v>-5.56</v>
       </c>
       <c r="L60" t="n">
-        <v>2.42</v>
+        <v>6.37</v>
       </c>
       <c r="M60" t="n">
-        <v>0.17</v>
+        <v>2.04</v>
       </c>
       <c r="N60" t="n">
-        <v>1.06</v>
+        <v>3.74</v>
       </c>
       <c r="O60" t="n">
         <v>2.32</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>5.82</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45980.55208333334</v>
+        <v>45981.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>5074</v>
+        <v>5140.5</v>
       </c>
       <c r="I61" t="n">
         <v>5089.577092075646</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.37</v>
+        <v>-2.7</v>
       </c>
       <c r="L61" t="n">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
       <c r="M61" t="n">
         <v>0.64</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>3.91</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45999.38541666666</v>
+        <v>45999.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>5103</v>
+        <v>5051</v>
       </c>
       <c r="I62" t="n">
         <v>5054.224944439396</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.73</v>
+        <v>-1.74</v>
       </c>
       <c r="L62" t="n">
         <v>2.26</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>3.92</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46002.38541666666</v>
+        <v>46002.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>5218</v>
+        <v>5254</v>
       </c>
       <c r="I63" t="n">
         <v>5231.364032519767</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.31</v>
+        <v>-4.02</v>
       </c>
       <c r="L63" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="M63" t="n">
         <v>0.03</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>4.05</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46030.38541666666</v>
+        <v>46030.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>5196.5</v>
+        <v>5036</v>
       </c>
       <c r="I64" t="n">
         <v>5093.90379104743</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.09</v>
+        <v>-4.15</v>
       </c>
       <c r="L64" t="n">
-        <v>3.4</v>
+        <v>5.15</v>
       </c>
       <c r="M64" t="n">
         <v>0.22</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.14</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>4777</v>
+        <v>5036</v>
       </c>
       <c r="I65" t="n">
         <v>4921.106060152772</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>3.22</v>
@@ -4146,7 +4925,7 @@
         <v>0.28</v>
       </c>
       <c r="N65" t="n">
-        <v>1.72</v>
+        <v>5.51</v>
       </c>
       <c r="O65" t="n">
         <v>-5.07</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.81</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>6299</v>
+        <v>5997</v>
       </c>
       <c r="I66" t="n">
         <v>5999.434890190012</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K66" t="n">
-        <v>25.08</v>
+        <v>19.08</v>
       </c>
       <c r="L66" t="n">
         <v>5.68</v>
@@ -4203,7 +4994,7 @@
         <v>3.96</v>
       </c>
       <c r="N66" t="n">
-        <v>2.72</v>
+        <v>4.19</v>
       </c>
       <c r="O66" t="n">
         <v>5.51</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>8.98</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>6270</v>
+        <v>6569</v>
       </c>
       <c r="I67" t="n">
         <v>6369.105954539848</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.55</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>4.89</v>
+        <v>9.59</v>
       </c>
       <c r="M67" t="n">
         <v>3.43</v>
       </c>
       <c r="N67" t="n">
-        <v>1.91</v>
+        <v>4.77</v>
       </c>
       <c r="O67" t="n">
         <v>-4.19</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46149.55208333334</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>7188</v>
+        <v>7048</v>
       </c>
       <c r="I68" t="n">
         <v>7082.260824217369</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K68" t="n">
-        <v>9.42</v>
+        <v>7.29</v>
       </c>
       <c r="L68" t="n">
         <v>3.03</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>7.4</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>6676.5</v>
+        <v>6771</v>
       </c>
       <c r="I69" t="n">
         <v>6765.920628328204</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K69" t="n">
-        <v>5.27</v>
+        <v>3.93</v>
       </c>
       <c r="L69" t="n">
         <v>2.3</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>6.22</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46183.38541666666</v>
+        <v>46183.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>6852</v>
+        <v>6800</v>
       </c>
       <c r="I70" t="n">
         <v>6824.398622256169</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>1.2</v>
+        <v>0.43</v>
       </c>
       <c r="L70" t="n">
         <v>0.86</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>6.19</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46190.38541666666</v>
+        <v>46190.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>7048.5</v>
+        <v>7165</v>
       </c>
       <c r="I71" t="n">
         <v>7092.722979544767</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.65</v>
+        <v>-5.37</v>
       </c>
       <c r="L71" t="n">
-        <v>4.11</v>
+        <v>5.7</v>
       </c>
       <c r="M71" t="n">
         <v>1.46</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>5.65</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46204.38541666666</v>
+        <v>46204.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>6985</v>
+        <v>6931.5</v>
       </c>
       <c r="I72" t="n">
         <v>6932.470666040021</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K72" t="n">
-        <v>-2.51</v>
+        <v>-3.26</v>
       </c>
       <c r="L72" t="n">
         <v>3.89</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>5.68</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46217.55208333334</v>
+        <v>46218.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>6910</v>
+        <v>7205</v>
       </c>
       <c r="I73" t="n">
         <v>7124.015570499531</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>0.31</v>
+        <v>-3.95</v>
       </c>
       <c r="L73" t="n">
-        <v>2.53</v>
+        <v>4.58</v>
       </c>
       <c r="M73" t="n">
         <v>0.6</v>
       </c>
       <c r="N73" t="n">
-        <v>1.64</v>
+        <v>4.63</v>
       </c>
       <c r="O73" t="n">
         <v>-1.32</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>7.1</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>7455</v>
+        <v>7376</v>
       </c>
       <c r="I74" t="n">
         <v>7384.021109040326</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K74" t="n">
-        <v>3.47</v>
+        <v>2.37</v>
       </c>
       <c r="L74" t="n">
         <v>3.87</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>78</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6821,7 +7728,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.3</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="6">
@@ -6831,7 +7738,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="7">
@@ -6841,7 +7748,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85.2</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -6851,7 +7758,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6861,7 +7768,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -6871,7 +7778,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43.9</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="11">
@@ -6911,7 +7818,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="15">
@@ -6921,7 +7828,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.88</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="16">
@@ -6931,7 +7838,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.67</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="17">
@@ -6941,7 +7848,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34.58</v>
+        <v>29.14</v>
       </c>
     </row>
     <row r="18">
@@ -6951,7 +7858,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.9</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="19">
@@ -6961,7 +7868,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.2</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="20">
@@ -6971,7 +7878,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.87</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="21">
@@ -6981,7 +7888,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.13</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="22">
@@ -6991,7 +7898,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -7001,7 +7908,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -7011,7 +7918,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="25">
@@ -7031,7 +7938,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.03</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="27">
@@ -7041,7 +7948,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.17</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="28">
@@ -7051,7 +7958,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
